--- a/checklist_forms/032_quality_assurance_check_form--checklist_forms.xlsx
+++ b/checklist_forms/032_quality_assurance_check_form--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>test_form</t>
+          <t>test_form_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Test Form</t>
+          <t>Test Form 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>test_form_2</t>
+          <t>test_form_2_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Test Form 2</t>
+          <t>Test Form 2 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_form_2</t>
+          <t>test_form_2_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Test Form 2</t>
+          <t>Test Form 2 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>quality_assurance_check_form</t>
+          <t>quality_assurance_check_form_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quality Assurance Check Form</t>
+          <t>Quality Assurance Check Form 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_operating_procedure_test</t>
+          <t>standard_operating_procedure_test_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Standard Operating Procedure Test</t>
+          <t>Standard Operating Procedure Test 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,19 +1284,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>test_form_choices</t>
+          <t>test_form_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>test_form_choices</t>
+          <t>test_form_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>test_form_2_choices</t>
+          <t>test_form_2_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>test_form_2_choices</t>
+          <t>test_form_2_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>test_form_2_choices</t>
+          <t>test_form_2_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>test_form_2_choices</t>
+          <t>test_form_2_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1534,34 +1534,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quality_assurance_check_form_choices</t>
+          <t>quality_assurance_check_form_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'1'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': '1'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>quality_assurance_check_form_choices</t>
+          <t>quality_assurance_check_form_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'2'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': '2'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
